--- a/artfynd/A 37815-2025 artfynd.xlsx
+++ b/artfynd/A 37815-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130181381</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130181358</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>130181398</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37815-2025 artfynd.xlsx
+++ b/artfynd/A 37815-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130181381</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130181358</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>130181398</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37815-2025 artfynd.xlsx
+++ b/artfynd/A 37815-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130181381</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130181358</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>130181398</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
